--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_14-04-2026.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_14-04-2026.xlsx
@@ -513,17 +513,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£12.76</t>
+          <t>£12.33</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£12.76</t>
+          <t>£12.33</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£12.76</t>
+          <t>£12.33</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -585,17 +585,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£14.51</t>
+          <t>£14.06</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£14.51</t>
+          <t>£14.06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£14.51</t>
+          <t>£14.06</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>£13.99</t>
+          <t>£15.39</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -657,17 +657,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£18.51</t>
+          <t>£18.33</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£18.51</t>
+          <t>£18.33</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£18.51</t>
+          <t>£18.33</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>£16.97</t>
+          <t>£18.67</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -729,17 +729,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£18.92</t>
+          <t>£18.44</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£18.92</t>
+          <t>£18.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£18.92</t>
+          <t>£18.44</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>£19.53</t>
+          <t>£21.48</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -801,17 +801,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£23.91</t>
+          <t>£23.65</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£23.91</t>
+          <t>£23.65</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£23.91</t>
+          <t>£23.65</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>£23.24</t>
+          <t>£25.56</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>£25.48</t>
+          <t>£28.03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>£25.62</t>
+          <t>£28.18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>£28.06</t>
+          <t>£30.87</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>£31.30</t>
+          <t>£34.43</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>£32.79</t>
+          <t>£36.07</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>£37.65</t>
+          <t>£41.42</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1305,17 +1305,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£40.49</t>
+          <t>£40.15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£40.49</t>
+          <t>£40.15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£40.49</t>
+          <t>£40.15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>£42.74</t>
+          <t>£47.01</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1377,17 +1377,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£49.75</t>
+          <t>£47.85</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£49.75</t>
+          <t>£47.85</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£49.75</t>
+          <t>£47.85</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>£44.00</t>
+          <t>£48.40</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1449,17 +1449,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£49.76</t>
+          <t>£49.00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£49.76</t>
+          <t>£49.00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>£49.76</t>
+          <t>£49.00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>£51.74</t>
+          <t>£56.91</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>£48.20</t>
+          <t>£53.02</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
